--- a/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
+++ b/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\IdeaProjects\lapr2\docs\sprint1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcapa\IdeaProjects\sem2-pi24.25-G092-repo\docs\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6BC235-E92F-495A-9ED0-1EC3FC8FB8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A56ABCE-08C0-4975-BFC6-C78A9D551D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -34,8 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="53">
   <si>
     <t>TeamID #</t>
   </si>
@@ -61,9 +59,6 @@
   </si>
   <si>
     <t>List A</t>
-  </si>
-  <si>
-    <t>Student 4</t>
   </si>
   <si>
     <t>Student 6</t>
@@ -1079,7 +1074,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Instructions"/>
@@ -1448,33 +1443,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="6.296875" customWidth="1"/>
+    <col min="2" max="2" width="6.25" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="7.8984375" customWidth="1"/>
+    <col min="4" max="12" width="7.875" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1483,13 +1478,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:13" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:13" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="E8" s="58" t="s">
@@ -1504,7 +1499,7 @@
       <c r="L8" s="59"/>
       <c r="M8" s="60"/>
     </row>
-    <row r="9" spans="1:13" ht="105.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="105.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="29">
@@ -1519,9 +1514,9 @@
         <f>C12</f>
         <v>1241166</v>
       </c>
-      <c r="G9" s="30" t="str">
+      <c r="G9" s="30">
         <f>C13</f>
-        <v>Student 4</v>
+        <v>1241285</v>
       </c>
       <c r="H9" s="30">
         <f>C14</f>
@@ -1543,7 +1538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="55" t="s">
         <v>5</v>
       </c>
@@ -1563,7 +1558,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="6">
         <v>1241176</v>
@@ -1581,7 +1576,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="6">
         <v>1241166</v>
@@ -1599,25 +1594,35 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
-      <c r="C13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="24"/>
+      <c r="C13" s="6">
+        <v>1241285</v>
+      </c>
+      <c r="D13" s="6">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6">
+        <v>5</v>
+      </c>
+      <c r="F13" s="7">
+        <v>5</v>
+      </c>
+      <c r="G13" s="53">
+        <v>5</v>
+      </c>
+      <c r="H13" s="24">
+        <v>5</v>
+      </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="36" t="e">
+      <c r="L13" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="6">
         <v>1220804</v>
@@ -1645,10 +1650,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="56"/>
       <c r="C15" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -1663,10 +1668,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="56"/>
       <c r="C16" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1681,10 +1686,10 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57"/>
       <c r="C17" s="28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
@@ -1699,7 +1704,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
       <c r="C18" s="32" t="s">
         <v>4</v>
@@ -1738,9 +1743,9 @@
       </c>
       <c r="L18" s="38"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="43"/>
       <c r="C20" s="43"/>
@@ -1754,9 +1759,9 @@
       <c r="K20" s="43"/>
       <c r="L20" s="44"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="46"/>
       <c r="C21" s="46"/>
@@ -1770,9 +1775,9 @@
       <c r="K21" s="46"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="46"/>
       <c r="C22" s="46"/>
@@ -1786,9 +1791,9 @@
       <c r="K22" s="46"/>
       <c r="L22" s="47"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="46"/>
       <c r="C23" s="46"/>
@@ -1802,7 +1807,7 @@
       <c r="K23" s="46"/>
       <c r="L23" s="47"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="46"/>
@@ -1816,9 +1821,9 @@
       <c r="K24" s="46"/>
       <c r="L24" s="47"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
@@ -1832,12 +1837,12 @@
       <c r="K25" s="46"/>
       <c r="L25" s="47"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="45">
         <v>0</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="46"/>
@@ -1850,12 +1855,12 @@
       <c r="K26" s="46"/>
       <c r="L26" s="47"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="45">
         <v>1</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="46"/>
@@ -1868,12 +1873,12 @@
       <c r="K27" s="46"/>
       <c r="L27" s="47"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="45">
         <v>2</v>
       </c>
       <c r="B28" s="46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="46"/>
       <c r="D28" s="46"/>
@@ -1886,12 +1891,12 @@
       <c r="K28" s="46"/>
       <c r="L28" s="47"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="45">
         <v>3</v>
       </c>
       <c r="B29" s="46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="46"/>
@@ -1904,12 +1909,12 @@
       <c r="K29" s="46"/>
       <c r="L29" s="47"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="45">
         <v>4</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="46"/>
       <c r="D30" s="46"/>
@@ -1922,12 +1927,12 @@
       <c r="K30" s="46"/>
       <c r="L30" s="47"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="45">
         <v>5</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="46"/>
@@ -1940,7 +1945,7 @@
       <c r="K31" s="46"/>
       <c r="L31" s="47"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="50"/>
       <c r="B32" s="51"/>
       <c r="C32" s="51"/>
@@ -1973,32 +1978,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="20.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="10" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="55" t="s">
+      <c r="B3" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="C3" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="D3" s="61" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" s="61" t="s">
-        <v>21</v>
       </c>
       <c r="E3" s="9">
         <v>0</v>
@@ -2019,109 +2024,109 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="56"/>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
       <c r="D4" s="62"/>
       <c r="E4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56"/>
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
       <c r="D5" s="62"/>
       <c r="E5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="G5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="I5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="J5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="40"/>
       <c r="E6" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="H6" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="I6" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="21" t="s">
-        <v>32</v>
-      </c>
       <c r="J6" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="40"/>
       <c r="E7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J7" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="18">
         <v>1220804</v>
@@ -2131,157 +2136,161 @@
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J8" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="40"/>
       <c r="E9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J9" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+        <v>45</v>
+      </c>
+      <c r="B10" s="18">
+        <v>1241285</v>
+      </c>
+      <c r="C10" s="18">
+        <v>5</v>
+      </c>
       <c r="D10" s="40"/>
       <c r="E10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J10" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="40"/>
       <c r="E11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J11" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="40"/>
       <c r="E12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J12" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="40"/>
       <c r="E13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J13" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="18">
         <v>1220804</v>
@@ -2291,462 +2300,470 @@
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J14" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
+        <v>50</v>
+      </c>
+      <c r="B15" s="18">
+        <v>1241285</v>
+      </c>
+      <c r="C15" s="18">
+        <v>5</v>
+      </c>
       <c r="D15" s="40"/>
       <c r="E15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J15" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="40"/>
       <c r="E16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J16" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
+        <v>52</v>
+      </c>
+      <c r="B17" s="18">
+        <v>1241285</v>
+      </c>
+      <c r="C17" s="18">
+        <v>5</v>
+      </c>
       <c r="D17" s="40"/>
       <c r="E17" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J17" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="40"/>
       <c r="E18" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J18" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="40"/>
       <c r="E19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J19" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
       <c r="D20" s="40"/>
       <c r="E20" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="I20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J20" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
       <c r="D21" s="40"/>
       <c r="E21" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J21" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="40"/>
       <c r="E22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="I22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J22" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="40"/>
       <c r="E23" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J23" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="40"/>
       <c r="E24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="I24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J24" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="40"/>
       <c r="E25" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J25" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="40"/>
       <c r="E26" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J26" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="40"/>
       <c r="E27" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J27" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="40"/>
       <c r="E28" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J28" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="40"/>
       <c r="E29" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J29" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="40"/>
       <c r="E30" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J30" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="40"/>
       <c r="E31" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="J31" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="39"/>
       <c r="C32" s="18"/>
       <c r="D32" s="41"/>
       <c r="E32" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="G32" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="H32" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="I32" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="I32" s="16" t="s">
-        <v>32</v>
-      </c>
       <c r="J32" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2783,15 +2800,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005836243B3C47804EAF5FFDD9F066FCC7" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9d21ddf3f0b128e39c9d770c8c903166">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b0326308c339679ad994635f2c691325" ns2:_="">
     <xsd:import namespace="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
@@ -2975,6 +2983,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2982,14 +2999,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B77F7C-EE47-4FBD-B078-6536C1487A1E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3003,6 +3012,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
+++ b/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcapa\IdeaProjects\sem2-pi24.25-G092-repo\docs\sprint1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63eef7978e99d393/Documents/GitHub/sem2-pi24.25-G092-repo/docs/sprint1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A56ABCE-08C0-4975-BFC6-C78A9D551D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{3A56ABCE-08C0-4975-BFC6-C78A9D551D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E77BC892-D6A5-442D-B0A4-C9C08DF36A05}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -1074,7 +1074,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Instructions"/>
@@ -1443,33 +1443,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.25" customWidth="1"/>
+    <col min="2" max="2" width="6.19921875" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="7.875" customWidth="1"/>
+    <col min="4" max="12" width="7.8984375" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1478,13 +1478,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:13" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:13" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="E8" s="58" t="s">
@@ -1499,7 +1499,7 @@
       <c r="L8" s="59"/>
       <c r="M8" s="60"/>
     </row>
-    <row r="9" spans="1:13" ht="105.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="105.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="29">
@@ -1538,7 +1538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>5</v>
       </c>
@@ -1558,25 +1558,35 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56"/>
       <c r="C11" s="6">
         <v>1241176</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="D11" s="7">
+        <v>5</v>
+      </c>
+      <c r="E11" s="53">
+        <v>5</v>
+      </c>
+      <c r="F11" s="24">
+        <v>5</v>
+      </c>
+      <c r="G11" s="6">
+        <v>5</v>
+      </c>
+      <c r="H11" s="6">
+        <v>5</v>
+      </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="8"/>
-      <c r="L11" s="36" t="e">
+      <c r="L11" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="56"/>
       <c r="C12" s="6">
         <v>1241166</v>
@@ -1594,7 +1604,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56"/>
       <c r="C13" s="6">
         <v>1241285</v>
@@ -1622,7 +1632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="56"/>
       <c r="C14" s="6">
         <v>1220804</v>
@@ -1650,7 +1660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56"/>
       <c r="C15" s="6" t="s">
         <v>6</v>
@@ -1668,7 +1678,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="56"/>
       <c r="C16" s="6" t="s">
         <v>7</v>
@@ -1686,7 +1696,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="57"/>
       <c r="C17" s="28" t="s">
         <v>8</v>
@@ -1704,7 +1714,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
       <c r="C18" s="32" t="s">
         <v>4</v>
@@ -1743,7 +1753,7 @@
       </c>
       <c r="L18" s="38"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="42" t="s">
         <v>9</v>
       </c>
@@ -1759,7 +1769,7 @@
       <c r="K20" s="43"/>
       <c r="L20" s="44"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
         <v>35</v>
       </c>
@@ -1775,7 +1785,7 @@
       <c r="K21" s="46"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="48" t="s">
         <v>36</v>
       </c>
@@ -1791,7 +1801,7 @@
       <c r="K22" s="46"/>
       <c r="L22" s="47"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="45" t="s">
         <v>37</v>
       </c>
@@ -1807,7 +1817,7 @@
       <c r="K23" s="46"/>
       <c r="L23" s="47"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="46"/>
@@ -1821,7 +1831,7 @@
       <c r="K24" s="46"/>
       <c r="L24" s="47"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
         <v>38</v>
       </c>
@@ -1837,7 +1847,7 @@
       <c r="K25" s="46"/>
       <c r="L25" s="47"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="45">
         <v>0</v>
       </c>
@@ -1855,7 +1865,7 @@
       <c r="K26" s="46"/>
       <c r="L26" s="47"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="45">
         <v>1</v>
       </c>
@@ -1873,7 +1883,7 @@
       <c r="K27" s="46"/>
       <c r="L27" s="47"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="45">
         <v>2</v>
       </c>
@@ -1891,7 +1901,7 @@
       <c r="K28" s="46"/>
       <c r="L28" s="47"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="45">
         <v>3</v>
       </c>
@@ -1909,7 +1919,7 @@
       <c r="K29" s="46"/>
       <c r="L29" s="47"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="45">
         <v>4</v>
       </c>
@@ -1927,7 +1937,7 @@
       <c r="K30" s="46"/>
       <c r="L30" s="47"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="45">
         <v>5</v>
       </c>
@@ -1945,7 +1955,7 @@
       <c r="K31" s="46"/>
       <c r="L31" s="47"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="50"/>
       <c r="B32" s="51"/>
       <c r="C32" s="51"/>
@@ -1978,21 +1988,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="10" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
         <v>17</v>
       </c>
@@ -2024,7 +2034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="56"/>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -2048,7 +2058,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="56"/>
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
@@ -2072,12 +2082,16 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
+      <c r="B6" s="18">
+        <v>1241176</v>
+      </c>
+      <c r="C6" s="18">
+        <v>5</v>
+      </c>
       <c r="D6" s="40"/>
       <c r="E6" s="20" t="s">
         <v>27</v>
@@ -2098,7 +2112,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>42</v>
       </c>
@@ -2124,7 +2138,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
@@ -2154,12 +2168,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
+      <c r="B9" s="18">
+        <v>1241176</v>
+      </c>
+      <c r="C9" s="18">
+        <v>5</v>
+      </c>
       <c r="D9" s="40"/>
       <c r="E9" s="11" t="s">
         <v>27</v>
@@ -2180,7 +2198,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>45</v>
       </c>
@@ -2210,7 +2228,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>46</v>
       </c>
@@ -2236,7 +2254,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -2262,7 +2280,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
@@ -2288,7 +2306,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>49</v>
       </c>
@@ -2318,7 +2336,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>50</v>
       </c>
@@ -2348,7 +2366,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
@@ -2374,7 +2392,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>52</v>
       </c>
@@ -2404,7 +2422,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -2428,7 +2446,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -2452,7 +2470,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -2476,7 +2494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2500,7 +2518,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2524,7 +2542,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2548,7 +2566,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2572,7 +2590,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -2596,7 +2614,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -2620,7 +2638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -2644,7 +2662,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -2668,7 +2686,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -2692,7 +2710,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>40</v>
       </c>
@@ -2718,7 +2736,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -2742,7 +2760,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15"/>
       <c r="B32" s="39"/>
       <c r="C32" s="18"/>
@@ -2800,6 +2818,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005836243B3C47804EAF5FFDD9F066FCC7" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9d21ddf3f0b128e39c9d770c8c903166">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b0326308c339679ad994635f2c691325" ns2:_="">
     <xsd:import namespace="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
@@ -2983,22 +3016,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B77F7C-EE47-4FBD-B078-6536C1487A1E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3014,28 +3056,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
+++ b/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63eef7978e99d393/Documents/GitHub/sem2-pi24.25-G092-repo/docs/sprint1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaom\OneDrive\Ambiente de Trabalho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{3A56ABCE-08C0-4975-BFC6-C78A9D551D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E77BC892-D6A5-442D-B0A4-C9C08DF36A05}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B86D0BA4-DAE3-4349-ADF7-BF4A4AB75482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -1443,33 +1443,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="6.19921875" customWidth="1"/>
+    <col min="2" max="2" width="6.25" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="7.8984375" customWidth="1"/>
+    <col min="4" max="12" width="7.875" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1478,13 +1478,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:13" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:13" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="E8" s="58" t="s">
@@ -1499,7 +1499,7 @@
       <c r="L8" s="59"/>
       <c r="M8" s="60"/>
     </row>
-    <row r="9" spans="1:13" ht="105.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="105.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="29">
@@ -1538,7 +1538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="55" t="s">
         <v>5</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56"/>
       <c r="C11" s="6">
         <v>1241176</v>
@@ -1586,25 +1586,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56"/>
       <c r="C12" s="6">
         <v>1241166</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="6"/>
+      <c r="D12" s="6">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5</v>
+      </c>
+      <c r="F12" s="53">
+        <v>5</v>
+      </c>
+      <c r="G12" s="24">
+        <v>5</v>
+      </c>
+      <c r="H12" s="6">
+        <v>5</v>
+      </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
       <c r="K12" s="8"/>
-      <c r="L12" s="36" t="e">
+      <c r="L12" s="36">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56"/>
       <c r="C13" s="6">
         <v>1241285</v>
@@ -1632,7 +1642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56"/>
       <c r="C14" s="6">
         <v>1220804</v>
@@ -1660,7 +1670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="56"/>
       <c r="C15" s="6" t="s">
         <v>6</v>
@@ -1678,7 +1688,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="56"/>
       <c r="C16" s="6" t="s">
         <v>7</v>
@@ -1696,7 +1706,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="57"/>
       <c r="C17" s="28" t="s">
         <v>8</v>
@@ -1714,7 +1724,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
       <c r="C18" s="32" t="s">
         <v>4</v>
@@ -1753,7 +1763,7 @@
       </c>
       <c r="L18" s="38"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
         <v>9</v>
       </c>
@@ -1769,7 +1779,7 @@
       <c r="K20" s="43"/>
       <c r="L20" s="44"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="45" t="s">
         <v>35</v>
       </c>
@@ -1785,7 +1795,7 @@
       <c r="K21" s="46"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="48" t="s">
         <v>36</v>
       </c>
@@ -1801,7 +1811,7 @@
       <c r="K22" s="46"/>
       <c r="L22" s="47"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="45" t="s">
         <v>37</v>
       </c>
@@ -1817,7 +1827,7 @@
       <c r="K23" s="46"/>
       <c r="L23" s="47"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="46"/>
@@ -1831,7 +1841,7 @@
       <c r="K24" s="46"/>
       <c r="L24" s="47"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="49" t="s">
         <v>38</v>
       </c>
@@ -1847,7 +1857,7 @@
       <c r="K25" s="46"/>
       <c r="L25" s="47"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="45">
         <v>0</v>
       </c>
@@ -1865,7 +1875,7 @@
       <c r="K26" s="46"/>
       <c r="L26" s="47"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="45">
         <v>1</v>
       </c>
@@ -1883,7 +1893,7 @@
       <c r="K27" s="46"/>
       <c r="L27" s="47"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="45">
         <v>2</v>
       </c>
@@ -1901,7 +1911,7 @@
       <c r="K28" s="46"/>
       <c r="L28" s="47"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="45">
         <v>3</v>
       </c>
@@ -1919,7 +1929,7 @@
       <c r="K29" s="46"/>
       <c r="L29" s="47"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="45">
         <v>4</v>
       </c>
@@ -1937,7 +1947,7 @@
       <c r="K30" s="46"/>
       <c r="L30" s="47"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="45">
         <v>5</v>
       </c>
@@ -1955,7 +1965,7 @@
       <c r="K31" s="46"/>
       <c r="L31" s="47"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="50"/>
       <c r="B32" s="51"/>
       <c r="C32" s="51"/>
@@ -1988,21 +1998,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="20.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="10" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="55" t="s">
         <v>17</v>
       </c>
@@ -2034,7 +2044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="56"/>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -2058,7 +2068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56"/>
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
@@ -2082,7 +2092,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>41</v>
       </c>
@@ -2112,12 +2122,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="B7" s="18">
+        <v>1241166</v>
+      </c>
+      <c r="C7" s="18">
+        <v>5</v>
+      </c>
       <c r="D7" s="40"/>
       <c r="E7" s="11" t="s">
         <v>27</v>
@@ -2138,7 +2152,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
@@ -2168,7 +2182,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
@@ -2198,7 +2212,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>45</v>
       </c>
@@ -2228,7 +2242,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>46</v>
       </c>
@@ -2254,7 +2268,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -2280,12 +2294,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="B13" s="18">
+        <v>1241166</v>
+      </c>
+      <c r="C13" s="18">
+        <v>5</v>
+      </c>
       <c r="D13" s="40"/>
       <c r="E13" s="11" t="s">
         <v>27</v>
@@ -2306,7 +2324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>49</v>
       </c>
@@ -2336,7 +2354,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>50</v>
       </c>
@@ -2366,7 +2384,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
@@ -2392,7 +2410,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>52</v>
       </c>
@@ -2422,7 +2440,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -2446,7 +2464,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -2470,7 +2488,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -2494,7 +2512,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2518,7 +2536,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2542,7 +2560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2566,7 +2584,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2590,7 +2608,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -2614,7 +2632,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -2638,7 +2656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -2662,7 +2680,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -2686,7 +2704,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -2710,7 +2728,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>40</v>
       </c>
@@ -2736,7 +2754,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -2760,7 +2778,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="39"/>
       <c r="C32" s="18"/>
@@ -2818,18 +2836,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3017,6 +3035,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -3028,14 +3054,6 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
+++ b/docs/sprint1/PI-2024-25_Team-Self-Assessment_v05.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaom\OneDrive\Ambiente de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B86D0BA4-DAE3-4349-ADF7-BF4A4AB75482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD549D54-E054-490C-8369-5792F6A80A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -1443,33 +1443,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="6.25" customWidth="1"/>
+    <col min="2" max="2" width="6.19921875" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="7.875" customWidth="1"/>
+    <col min="4" max="12" width="7.8984375" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1478,13 +1478,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:13" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:13" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="E8" s="58" t="s">
@@ -1499,7 +1499,7 @@
       <c r="L8" s="59"/>
       <c r="M8" s="60"/>
     </row>
-    <row r="9" spans="1:13" ht="105.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="105.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="29">
@@ -1538,27 +1538,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="55" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="25">
         <v>1241323</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="D10" s="53">
+        <v>5</v>
+      </c>
+      <c r="E10" s="26">
+        <v>5</v>
+      </c>
+      <c r="F10" s="27">
+        <v>5</v>
+      </c>
+      <c r="G10" s="27">
+        <v>5</v>
+      </c>
+      <c r="H10" s="27">
+        <v>5</v>
+      </c>
       <c r="I10" s="27"/>
       <c r="J10" s="27"/>
       <c r="K10" s="25"/>
-      <c r="L10" s="35" t="e">
+      <c r="L10" s="35">
         <f t="shared" ref="L10:L17" si="0">AVERAGE(D10:K10)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="56"/>
       <c r="C11" s="6">
         <v>1241176</v>
@@ -1586,7 +1596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="56"/>
       <c r="C12" s="6">
         <v>1241166</v>
@@ -1614,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="56"/>
       <c r="C13" s="6">
         <v>1241285</v>
@@ -1642,7 +1652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="56"/>
       <c r="C14" s="6">
         <v>1220804</v>
@@ -1670,7 +1680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="56"/>
       <c r="C15" s="6" t="s">
         <v>6</v>
@@ -1688,7 +1698,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="56"/>
       <c r="C16" s="6" t="s">
         <v>7</v>
@@ -1706,7 +1716,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="57"/>
       <c r="C17" s="28" t="s">
         <v>8</v>
@@ -1724,7 +1734,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
       <c r="C18" s="32" t="s">
         <v>4</v>
@@ -1763,7 +1773,7 @@
       </c>
       <c r="L18" s="38"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="42" t="s">
         <v>9</v>
       </c>
@@ -1779,7 +1789,7 @@
       <c r="K20" s="43"/>
       <c r="L20" s="44"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
         <v>35</v>
       </c>
@@ -1795,7 +1805,7 @@
       <c r="K21" s="46"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="48" t="s">
         <v>36</v>
       </c>
@@ -1811,7 +1821,7 @@
       <c r="K22" s="46"/>
       <c r="L22" s="47"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="45" t="s">
         <v>37</v>
       </c>
@@ -1827,7 +1837,7 @@
       <c r="K23" s="46"/>
       <c r="L23" s="47"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="45"/>
       <c r="B24" s="46"/>
       <c r="C24" s="46"/>
@@ -1841,7 +1851,7 @@
       <c r="K24" s="46"/>
       <c r="L24" s="47"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
         <v>38</v>
       </c>
@@ -1857,7 +1867,7 @@
       <c r="K25" s="46"/>
       <c r="L25" s="47"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="45">
         <v>0</v>
       </c>
@@ -1875,7 +1885,7 @@
       <c r="K26" s="46"/>
       <c r="L26" s="47"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="45">
         <v>1</v>
       </c>
@@ -1893,7 +1903,7 @@
       <c r="K27" s="46"/>
       <c r="L27" s="47"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="45">
         <v>2</v>
       </c>
@@ -1911,7 +1921,7 @@
       <c r="K28" s="46"/>
       <c r="L28" s="47"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="45">
         <v>3</v>
       </c>
@@ -1929,7 +1939,7 @@
       <c r="K29" s="46"/>
       <c r="L29" s="47"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="45">
         <v>4</v>
       </c>
@@ -1947,7 +1957,7 @@
       <c r="K30" s="46"/>
       <c r="L30" s="47"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="45">
         <v>5</v>
       </c>
@@ -1965,7 +1975,7 @@
       <c r="K31" s="46"/>
       <c r="L31" s="47"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="50"/>
       <c r="B32" s="51"/>
       <c r="C32" s="51"/>
@@ -1998,21 +2008,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="20.09765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.5" customWidth="1"/>
     <col min="5" max="10" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="19" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
         <v>17</v>
       </c>
@@ -2044,7 +2054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="56"/>
       <c r="B4" s="64"/>
       <c r="C4" s="64"/>
@@ -2068,7 +2078,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="56"/>
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
@@ -2092,7 +2102,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>41</v>
       </c>
@@ -2122,7 +2132,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>42</v>
       </c>
@@ -2152,7 +2162,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>43</v>
       </c>
@@ -2182,7 +2192,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>44</v>
       </c>
@@ -2212,7 +2222,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>45</v>
       </c>
@@ -2242,12 +2252,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="B11" s="18">
+        <v>1241323</v>
+      </c>
+      <c r="C11" s="18">
+        <v>5</v>
+      </c>
       <c r="D11" s="40"/>
       <c r="E11" s="11" t="s">
         <v>27</v>
@@ -2268,12 +2282,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="18">
+        <v>1241323</v>
+      </c>
+      <c r="C12" s="18">
+        <v>5</v>
+      </c>
       <c r="D12" s="40"/>
       <c r="E12" s="11" t="s">
         <v>27</v>
@@ -2294,7 +2312,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
@@ -2324,7 +2342,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>49</v>
       </c>
@@ -2354,7 +2372,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>50</v>
       </c>
@@ -2384,12 +2402,16 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="B16" s="18">
+        <v>1241323</v>
+      </c>
+      <c r="C16" s="18">
+        <v>5</v>
+      </c>
       <c r="D16" s="40"/>
       <c r="E16" s="11" t="s">
         <v>27</v>
@@ -2410,7 +2432,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>52</v>
       </c>
@@ -2440,7 +2462,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -2464,7 +2486,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -2488,7 +2510,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -2512,7 +2534,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2536,7 +2558,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2560,7 +2582,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2584,7 +2606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -2608,7 +2630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -2632,7 +2654,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -2656,7 +2678,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -2680,7 +2702,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -2704,7 +2726,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
@@ -2728,7 +2750,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>40</v>
       </c>
@@ -2754,7 +2776,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
@@ -2778,7 +2800,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="15"/>
       <c r="B32" s="39"/>
       <c r="C32" s="18"/>
@@ -2836,18 +2858,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3035,14 +3057,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -3054,6 +3068,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="a1e3ca88-8ae5-4fd0-ba37-40ce669fcbb0"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
